--- a/data/gravel/Turner Nitrous Ti 2025.xlsx
+++ b/data/gravel/Turner Nitrous Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13D63F96-2893-2148-98B9-A15C357625AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD227E41-E754-B546-BFDD-6D3C5B4E3D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33980" yWindow="-23240" windowWidth="27260" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1384,6 +1384,9 @@
       <c r="A45" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="B45" s="1">
+        <v>120</v>
+      </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">

--- a/data/gravel/Turner Nitrous Ti 2025.xlsx
+++ b/data/gravel/Turner Nitrous Ti 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD227E41-E754-B546-BFDD-6D3C5B4E3D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6255827C-654F-7D46-A4C0-BB10DC8D6DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33980" yWindow="-23240" windowWidth="27260" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="107">
   <si>
     <t>brand</t>
   </si>
@@ -351,6 +351,9 @@
   </si>
   <si>
     <t>hardtail</t>
+  </si>
+  <si>
+    <t>https://turnerbikes.com/cdn/shop/files/Nitrous-side.jpg?v=1745624168&amp;width=1780</t>
   </si>
 </sst>
 </file>
@@ -791,6 +794,11 @@
         <v>78</v>
       </c>
     </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>

--- a/data/gravel/Turner Nitrous Ti 2025.xlsx
+++ b/data/gravel/Turner Nitrous Ti 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6255827C-654F-7D46-A4C0-BB10DC8D6DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B8A47F-5F7C-264F-97A2-A800E26F349D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33980" yWindow="-23240" windowWidth="27260" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11540" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="109">
   <si>
     <t>brand</t>
   </si>
@@ -354,6 +354,12 @@
   </si>
   <si>
     <t>https://turnerbikes.com/cdn/shop/files/Nitrous-side.jpg?v=1745624168&amp;width=1780</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Murrieta, California, USA</t>
   </si>
 </sst>
 </file>
@@ -747,7 +753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1578,6 +1584,14 @@
         <v>100</v>
       </c>
     </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Turner Nitrous Ti 2025.xlsx
+++ b/data/gravel/Turner Nitrous Ti 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B8A47F-5F7C-264F-97A2-A800E26F349D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{917856A3-19B2-9742-B97A-337BD0F8F321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11540" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28940" yWindow="-22960" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -344,9 +344,6 @@
     <t>a8:f33</t>
   </si>
   <si>
-    <t>estimated at ~530, which is 120 mm fork w 0% sag</t>
-  </si>
-  <si>
     <t>suspension</t>
   </si>
   <si>
@@ -360,6 +357,9 @@
   </si>
   <si>
     <t>Murrieta, California, USA</t>
+  </si>
+  <si>
+    <t>fox 120 mm fork w 30% sag</t>
   </si>
 </sst>
 </file>
@@ -802,7 +802,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -1106,29 +1106,37 @@
         <v>15</v>
       </c>
       <c r="C23" s="3">
-        <v>530</v>
+        <v>494</v>
       </c>
       <c r="D23" s="3">
-        <v>530</v>
+        <v>494</v>
       </c>
       <c r="E23" s="3">
-        <v>530</v>
+        <v>494</v>
       </c>
       <c r="F23" s="3">
-        <v>530</v>
+        <v>494</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
+      <c r="C24" s="3">
+        <v>44</v>
+      </c>
+      <c r="D24" s="3">
+        <v>44</v>
+      </c>
+      <c r="E24" s="3">
+        <v>44</v>
+      </c>
+      <c r="F24" s="3">
+        <v>44</v>
+      </c>
       <c r="G24" s="3"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
@@ -1316,7 +1324,7 @@
         <v>66</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>83</v>
@@ -1349,7 +1357,7 @@
         <v>68</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
@@ -1586,10 +1594,10 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Turner Nitrous Ti 2025.xlsx
+++ b/data/gravel/Turner Nitrous Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{917856A3-19B2-9742-B97A-337BD0F8F321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{029CC421-50E1-054B-BDD1-A35E28B3F087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28940" yWindow="-22960" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="115">
   <si>
     <t>brand</t>
   </si>
@@ -360,6 +360,24 @@
   </si>
   <si>
     <t>fox 120 mm fork w 30% sag</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -753,7 +771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1438,165 +1456,195 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>43</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52" s="1">
-        <v>30.9</v>
+        <v>111</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>45</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B54" s="1">
-        <v>38</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>47</v>
+        <v>114</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B56" s="1">
-        <v>180</v>
+        <v>42</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B57" s="1">
-        <v>160</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B58" s="1">
+        <v>30.9</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>72</v>
+        <v>46</v>
+      </c>
+      <c r="B60" s="1">
+        <v>38</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
+      </c>
+      <c r="B62" s="1">
+        <v>180</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B63" s="1">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B64" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B65" s="1">
-        <v>1</v>
+        <v>51</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
+      </c>
+      <c r="B69" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B70" s="1">
-        <v>2600</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
+      </c>
+      <c r="B71" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B76" s="1">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B80" s="1" t="s">
         <v>107</v>
       </c>
     </row>

--- a/data/gravel/Turner Nitrous Ti 2025.xlsx
+++ b/data/gravel/Turner Nitrous Ti 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{029CC421-50E1-054B-BDD1-A35E28B3F087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1305A96A-33E1-D947-BE36-5173025B5D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28940" yWindow="-22960" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="117">
   <si>
     <t>brand</t>
   </si>
@@ -245,9 +245,6 @@
     <t>yes</t>
   </si>
   <si>
-    <t>trail</t>
-  </si>
-  <si>
     <t>front_center</t>
   </si>
   <si>
@@ -341,9 +338,6 @@
     <t>threaded 73</t>
   </si>
   <si>
-    <t>a8:f33</t>
-  </si>
-  <si>
     <t>suspension</t>
   </si>
   <si>
@@ -359,9 +353,6 @@
     <t>Murrieta, California, USA</t>
   </si>
   <si>
-    <t>fox 120 mm fork w 30% sag</t>
-  </si>
-  <si>
     <t>head_tube_d</t>
   </si>
   <si>
@@ -378,6 +369,21 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>a8:f34</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>(Geo based on 120 fork)</t>
+  </si>
+  <si>
+    <t>120-130</t>
   </si>
 </sst>
 </file>
@@ -387,7 +393,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -441,6 +447,13 @@
       <sz val="14"/>
       <name val="Futura Medium"/>
     </font>
+    <font>
+      <i/>
+      <sz val="13"/>
+      <color rgb="FF666666"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -462,7 +475,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -475,6 +488,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -771,7 +785,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I80"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -783,7 +797,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -791,7 +805,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -815,12 +829,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -828,7 +842,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -836,19 +850,19 @@
         <v>6</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C8" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="E8" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="F8" s="9" t="s">
         <v>81</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>82</v>
       </c>
       <c r="G8" s="5"/>
     </row>
@@ -857,7 +871,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C9" s="11">
         <v>590</v>
@@ -877,7 +891,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C10" s="11">
         <v>370</v>
@@ -898,7 +912,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C11" s="11">
         <v>75</v>
@@ -919,7 +933,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C12" s="11">
         <v>85</v>
@@ -940,7 +954,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C13" s="11">
         <v>66.5</v>
@@ -961,7 +975,7 @@
         <v>18</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C14" s="11">
         <v>62</v>
@@ -982,7 +996,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C15" s="11">
         <v>435</v>
@@ -1003,7 +1017,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C16" s="11">
         <v>428</v>
@@ -1019,12 +1033,12 @@
       </c>
       <c r="H16" s="5"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C17" s="11">
         <v>610</v>
@@ -1040,12 +1054,12 @@
       </c>
       <c r="H17" s="5"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C18" s="11">
         <v>1140</v>
@@ -1061,12 +1075,12 @@
       </c>
       <c r="H18" s="5"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C19" s="11">
         <v>760</v>
@@ -1082,12 +1096,12 @@
       </c>
       <c r="H19" s="5"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C20" s="11">
         <v>240</v>
@@ -1103,15 +1117,15 @@
       </c>
       <c r="H20" s="5"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G21" s="3"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -1119,27 +1133,24 @@
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C23" s="3">
-        <v>494</v>
+        <v>530</v>
       </c>
       <c r="D23" s="3">
-        <v>494</v>
+        <v>530</v>
       </c>
       <c r="E23" s="3">
-        <v>494</v>
+        <v>530</v>
       </c>
       <c r="F23" s="3">
-        <v>494</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>16</v>
       </c>
@@ -1157,19 +1168,29 @@
       </c>
       <c r="G24" s="3"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+      <c r="C25" s="3">
+        <v>120</v>
+      </c>
+      <c r="D25" s="3">
+        <v>120</v>
+      </c>
+      <c r="E25" s="3">
+        <v>120</v>
+      </c>
+      <c r="F25" s="3">
+        <v>120</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>22</v>
+        <v>114</v>
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
@@ -1177,418 +1198,420 @@
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B30" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C30" s="1">
         <v>700</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D30" s="1">
         <v>700</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E30" s="1">
         <v>700</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F30" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B31" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C31" s="1">
         <v>2.4</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D31" s="1">
         <v>2.4</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E31" s="1">
         <v>2.4</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F31" s="1">
         <v>2.4</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B32" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C32" s="1">
         <v>2.6</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D32" s="1">
         <v>2.6</v>
       </c>
-      <c r="E31" s="1">
+      <c r="E32" s="1">
         <v>2.6</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F32" s="1">
         <v>2.6</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B33" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="6">
-        <f>C34*2.54</f>
+      <c r="C33" s="6">
+        <f>C35*2.54</f>
         <v>154.94</v>
       </c>
-      <c r="D32" s="6">
-        <f t="shared" ref="D32:F33" si="0">D34*2.54</f>
+      <c r="D33" s="6">
+        <f t="shared" ref="D33:F34" si="0">D35*2.54</f>
         <v>167.64000000000001</v>
       </c>
-      <c r="E32" s="6">
+      <c r="E33" s="6">
         <f t="shared" si="0"/>
         <v>177.8</v>
       </c>
-      <c r="F32" s="6">
+      <c r="F33" s="6">
         <f t="shared" si="0"/>
         <v>187.96</v>
-      </c>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C33" s="6">
-        <f>C35*2.54</f>
-        <v>167.64000000000001</v>
-      </c>
-      <c r="D33" s="6">
-        <f t="shared" si="0"/>
-        <v>177.8</v>
-      </c>
-      <c r="E33" s="6">
-        <f t="shared" si="0"/>
-        <v>187.96</v>
-      </c>
-      <c r="F33" s="6">
-        <f t="shared" si="0"/>
-        <v>198.12</v>
       </c>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
       <c r="I33" s="6"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="3">
+      <c r="A34" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34" s="6">
+        <f>C36*2.54</f>
+        <v>167.64000000000001</v>
+      </c>
+      <c r="D34" s="6">
+        <f t="shared" si="0"/>
+        <v>177.8</v>
+      </c>
+      <c r="E34" s="6">
+        <f t="shared" si="0"/>
+        <v>187.96</v>
+      </c>
+      <c r="F34" s="6">
+        <f t="shared" si="0"/>
+        <v>198.12</v>
+      </c>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C35" s="3">
         <v>61</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D35" s="3">
         <v>66</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E35" s="3">
         <v>70</v>
       </c>
-      <c r="F34" s="3">
+      <c r="F35" s="3">
         <v>74</v>
       </c>
-      <c r="G34" s="3"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C35" s="4">
-        <v>66</v>
-      </c>
-      <c r="D35" s="4">
-        <v>70</v>
-      </c>
-      <c r="E35" s="4">
-        <v>74</v>
-      </c>
-      <c r="F35" s="4">
-        <v>78</v>
-      </c>
-      <c r="G35" s="4"/>
+      <c r="G35" s="3"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" s="4">
         <v>66</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="G36" s="8"/>
+      <c r="D36" s="4">
+        <v>70</v>
+      </c>
+      <c r="E36" s="4">
+        <v>74</v>
+      </c>
+      <c r="F36" s="4">
+        <v>78</v>
+      </c>
+      <c r="G36" s="4"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
+        <v>102</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="G37" s="8"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>103</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B42" s="1">
-        <v>2.6</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
+      </c>
+      <c r="B43" s="1">
+        <v>2.6</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B44" s="1">
-        <v>120</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="1">
-        <v>120</v>
+        <v>36</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
+      </c>
+      <c r="B46" s="1">
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="1">
-        <v>148</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" s="1">
-        <v>110</v>
+        <v>148</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>109</v>
+        <v>41</v>
+      </c>
+      <c r="B50" s="1">
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B58" s="1">
-        <v>30.9</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
+      </c>
+      <c r="B59" s="1">
+        <v>30.9</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B60" s="1">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
+      </c>
+      <c r="B61" s="1">
+        <v>38</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B62" s="1">
-        <v>180</v>
+        <v>47</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B63" s="1">
-        <v>160</v>
+        <v>180</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
+      </c>
+      <c r="B64" s="1">
+        <v>160</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B69" s="1">
-        <v>2</v>
+        <v>54</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B70" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B71" s="1">
         <v>1</v>
@@ -1596,56 +1619,64 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
+      </c>
+      <c r="B72" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B76" s="1">
-        <v>2600</v>
+        <v>61</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
+      </c>
+      <c r="B77" s="1">
+        <v>2600</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>106</v>
+        <v>65</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>107</v>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
